--- a/AAII_Financials/Yearly/DEC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DEC_YR_FIN.xlsx
@@ -1056,7 +1056,7 @@
         <v>-3300</v>
       </c>
       <c r="E20" s="3">
-        <v>-2300</v>
+        <v>-1200</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1089,7 +1089,7 @@
         <v>898300</v>
       </c>
       <c r="E21" s="3">
-        <v>171000</v>
+        <v>169900</v>
       </c>
       <c r="F21" s="3">
         <v>1357300</v>
@@ -1452,7 +1452,7 @@
         <v>3300</v>
       </c>
       <c r="E32" s="3">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
